--- a/output/pdf_financials_xlsx/AEP.xlsx
+++ b/output/pdf_financials_xlsx/AEP.xlsx
@@ -1975,25 +1975,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017491</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.158106</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007414</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000197</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.234848</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.867384</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.593762</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>8.947182</v>
@@ -2008,7 +2008,7 @@
         <v>13.128028</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.392786</v>
       </c>
     </row>
     <row r="35">
@@ -2061,25 +2061,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017491</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.215132</v>
+        <v>0.373238</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.007414</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000197</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.234848</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.867384</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.593762</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>8.947182</v>
@@ -2094,7 +2094,7 @@
         <v>13.128028</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.392786</v>
       </c>
     </row>
     <row r="37">
@@ -2577,25 +2577,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.212635</v>
+        <v>0.195144</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.186966</v>
+        <v>0.02886</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.010563</v>
+        <v>0.003149</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001448</v>
+        <v>0.001251</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.237214</v>
+        <v>0.002366</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.24926</v>
+        <v>0.381876</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.763196</v>
+        <v>0.169434</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.259066</v>
@@ -2610,7 +2610,7 @@
         <v>1.510393</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.586817</v>
+        <v>1.194031</v>
       </c>
     </row>
     <row r="49">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">

--- a/output/pdf_financials_xlsx/AEP.xlsx
+++ b/output/pdf_financials_xlsx/AEP.xlsx
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.008595999999999999</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.020628</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E406" s="5" t="n">

--- a/output/pdf_financials_xlsx/AEP.xlsx
+++ b/output/pdf_financials_xlsx/AEP.xlsx
@@ -1118,7 +1118,7 @@
         <v>-1.025508</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-5.073437</v>
+        <v>-4.949681</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>0.286465</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.118672</v>
+        <v>-0.005084</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1687,7 +1687,7 @@
         <v>-1.025508</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.073437</v>
+        <v>-4.949681</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>-0.65329</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.511553</v>
+        <v>-4.387797</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>-8.089249825440158</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-38.90216894181825</v>
+        <v>-37.83504708387628</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>-27.93396053468135</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-2.339084924085979</v>
+        <v>-0.1027136900337618</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -2245,28 +2245,28 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.001049</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.013751</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.058925</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.055714</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.039926</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.083925</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.490073</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.656708</v>
       </c>
     </row>
     <row r="41">
@@ -2288,28 +2288,28 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.893104</v>
+        <v>0.894153</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.008773</v>
+        <v>2.022524</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>4.055629</v>
+        <v>4.114554</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6.730912</v>
+        <v>6.786626</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.825034</v>
+        <v>5.86496</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>6.709146</v>
+        <v>6.793071</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>7.986127</v>
+        <v>8.4762</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>9.150876</v>
+        <v>9.807584</v>
       </c>
     </row>
     <row r="42">
@@ -2589,28 +2589,28 @@
         <v>0.001251</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.002366</v>
+        <v>0.001317</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.381876</v>
+        <v>0.368125</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.169434</v>
+        <v>0.110509</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.259066</v>
+        <v>0.203352</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.362712</v>
+        <v>0.322786</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.53292</v>
+        <v>2.448995</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.510393</v>
+        <v>1.02032</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.194031</v>
+        <v>0.537323</v>
       </c>
     </row>
     <row r="49">
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.233992</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.273406</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.227086</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.139065</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.517115</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.091902</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.711022</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.293663</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.573251</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1.186226</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.686808</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>2.153254</v>
       </c>
     </row>
     <row r="65">
@@ -3446,28 +3446,28 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0659</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.13525</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.850565</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.858548</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.305627</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.59761</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.321946</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.440046</v>
       </c>
     </row>
     <row r="68">
@@ -3575,10 +3575,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.303573</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.568069</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -3618,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.303573</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.568069</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0</v>
@@ -3790,10 +3790,10 @@
         <v>0.220125</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.666047</v>
+        <v>1.362474</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.766923</v>
+        <v>2.198854</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>8.794705</v>
@@ -4012,15 +4012,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>-0.714474334533644</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1535961328758816</v>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
@@ -4906,16 +4902,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.019088</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.011158</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.018991</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000249</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>-0.398137</v>
@@ -5121,16 +5117,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.30437</v>
+        <v>-0.323458</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.100636</v>
+        <v>0.111794</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.039578</v>
+        <v>0.058569</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.06106</v>
+        <v>0.060811</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.468796</v>
@@ -5308,10 +5304,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.020716</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.005154</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5348,19 +5344,19 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.120755</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035917</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-1.323129</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-3.647724</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -5511,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.199421</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.09209100000000001</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -6367,19 +6363,19 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.120755</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035917</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-1.323129</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-3.647724</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -6414,10 +6410,10 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>0.830741</v>
+        <v>0.709986</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.6190020000000001</v>
+        <v>-0.654919</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -6425,10 +6421,10 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>9.578537000000001</v>
+        <v>8.255407999999999</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>11.296269</v>
+        <v>7.648545</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>4.484011</v>
@@ -16810,7 +16806,11 @@
           <t>Current portion of lease obligations 18 1,000,867</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -18586,7 +18586,11 @@
           <t>Current portion of lease obligations 15</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -22098,7 +22102,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -23750,7 +23758,11 @@
           <t>Shares issued for cash (Note 17b)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -25086,7 +25098,11 @@
           <t>Shares issued for cash (Note 13b)</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -25622,7 +25638,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -26666,7 +26686,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -27412,7 +27436,11 @@
           <t>Deferred tax expense (recovery) 10,877</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -27794,7 +27822,11 @@
           <t>Accretion expense -</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -29848,7 +29880,11 @@
           <t>Shares issued for cash -</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -30998,7 +31034,11 @@
           <t>Accretion expense 5,154</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -32546,7 +32586,11 @@
           <t>Shares issued for cash 4,132,000</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -33712,7 +33756,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -34624,7 +34672,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -35908,7 +35960,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E390" s="5" t="n">
         <v>-0.019088</v>
       </c>
@@ -36198,7 +36254,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -39660,7 +39720,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -41050,7 +41114,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -41588,7 +41656,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -45680,7 +45752,11 @@
           <t>Deferred income tax recovery 14 769,312</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
